--- a/templates/INTERNAL_TRACE_WORKBOOK.xlsx
+++ b/templates/INTERNAL_TRACE_WORKBOOK.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使用说明" sheetId="1" r:id="Rb4056542416e4e9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_实验总台账" sheetId="2" r:id="R4a88842998cd4332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_附件索引" sheetId="3" r:id="R8817d5aff1774c8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_图片粘贴区" sheetId="4" r:id="Rbae65a4a97644faf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_修改记录" sheetId="5" r:id="R6aa2ec28e6d046ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_复核记录" sheetId="6" r:id="Re65678cafe96436b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验01_表面粗糙度" sheetId="7" r:id="R1ca0a3665d0e4045"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验02_裂纹萌生" sheetId="8" r:id="R7e7433cb701b421c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验03_X射线内部质量" sheetId="9" r:id="R18507ba25cb04c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验04_翘曲变形" sheetId="10" r:id="R4c35545f49e949fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验05_热膨胀系数" sheetId="11" r:id="Ra8a43f267a5147dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验06_耐急冷急热" sheetId="12" r:id="R9bfa2349db8a4362"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验07_弯曲性能" sheetId="13" r:id="Rce50cb67c1874519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验08_维氏硬度" sheetId="14" r:id="Rf36b9f2211f3414b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验09_厚度测量" sheetId="15" r:id="R45a3c48c20e94dac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验10_色稳定性" sheetId="16" r:id="Rc6f54aba90a64124"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_使用说明" sheetId="1" r:id="R4c91403e1e9342d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_实验总台账" sheetId="2" r:id="R64100069a88847d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_附件索引" sheetId="3" r:id="Rb294b6a725734052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_图片粘贴区" sheetId="4" r:id="R27a81a5590e942c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_修改记录" sheetId="5" r:id="R4943ee0fc1c24164"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_复核记录" sheetId="6" r:id="R17a2f2be8d66411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验01_表面粗糙度" sheetId="7" r:id="Rb462a9c3d1ab478a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验02_裂纹萌生" sheetId="8" r:id="R9d7d8a3652644ec0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验03_X射线内部质量" sheetId="9" r:id="Rc83f2ba7d4b245d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验04_翘曲变形" sheetId="10" r:id="Rb46225d10c36426a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验05_热膨胀系数" sheetId="11" r:id="R3555e302d47b4a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验06_耐急冷急热" sheetId="12" r:id="Rc1495e37f6e048a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验07_弯曲性能" sheetId="13" r:id="R16114997e41b4710"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验08_维氏硬度" sheetId="14" r:id="Rd74609d6e7ec4916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验09_厚度测量" sheetId="15" r:id="R6c1be239e3ca48ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实验10_色稳定性" sheetId="16" r:id="R0eb0bb9e12fc463b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -8385,6 +8385,14 @@
       <x:c r="P2" s="5"/>
       <x:c r="Q2" s="5"/>
     </x:row>
+    <x:row r="3">
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3"/>
+      <x:c r="N3"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="33" t="str">
         <x:v>附件ID</x:v>
@@ -8417,26 +8425,24 @@
         <x:v>上传/导出人</x:v>
       </x:c>
       <x:c r="K4" s="33" t="str">
-        <x:v>设备或软件</x:v>
+        <x:v>实验步骤</x:v>
       </x:c>
       <x:c r="L4" s="33" t="str">
-        <x:v>实验步骤</x:v>
+        <x:v>内容说明</x:v>
       </x:c>
       <x:c r="M4" s="33" t="str">
-        <x:v>内容说明</x:v>
+        <x:v>原始/处理文件</x:v>
       </x:c>
       <x:c r="N4" s="33" t="str">
-        <x:v>原始/处理文件</x:v>
+        <x:v>关联原文件ID</x:v>
       </x:c>
       <x:c r="O4" s="33" t="str">
-        <x:v>关联原文件ID</x:v>
+        <x:v>SHA-256校验值</x:v>
       </x:c>
       <x:c r="P4" s="33" t="str">
-        <x:v>SHA-256校验值</x:v>
-      </x:c>
-      <x:c r="Q4" s="33" t="str">
         <x:v>复核状态</x:v>
       </x:c>
+      <x:c r="Q4" s="33"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="36"/>
@@ -11287,6 +11293,374 @@
       <x:c r="O154" s="36"/>
       <x:c r="P154" s="36"/>
       <x:c r="Q154" s="36"/>
+    </x:row>
+    <x:row r="155">
+      <x:c r="K155"/>
+      <x:c r="L155"/>
+      <x:c r="M155"/>
+      <x:c r="N155"/>
+      <x:c r="O155"/>
+      <x:c r="P155"/>
+    </x:row>
+    <x:row r="156">
+      <x:c r="K156"/>
+      <x:c r="L156"/>
+      <x:c r="M156"/>
+      <x:c r="N156"/>
+      <x:c r="O156"/>
+      <x:c r="P156"/>
+    </x:row>
+    <x:row r="157">
+      <x:c r="K157"/>
+      <x:c r="L157"/>
+      <x:c r="M157"/>
+      <x:c r="N157"/>
+      <x:c r="O157"/>
+      <x:c r="P157"/>
+    </x:row>
+    <x:row r="158">
+      <x:c r="K158"/>
+      <x:c r="L158"/>
+      <x:c r="M158"/>
+      <x:c r="N158"/>
+      <x:c r="O158"/>
+      <x:c r="P158"/>
+    </x:row>
+    <x:row r="159">
+      <x:c r="K159"/>
+      <x:c r="L159"/>
+      <x:c r="M159"/>
+      <x:c r="N159"/>
+      <x:c r="O159"/>
+      <x:c r="P159"/>
+    </x:row>
+    <x:row r="160">
+      <x:c r="K160"/>
+      <x:c r="L160"/>
+      <x:c r="M160"/>
+      <x:c r="N160"/>
+      <x:c r="O160"/>
+      <x:c r="P160"/>
+    </x:row>
+    <x:row r="161">
+      <x:c r="K161"/>
+      <x:c r="L161"/>
+      <x:c r="M161"/>
+      <x:c r="N161"/>
+      <x:c r="O161"/>
+      <x:c r="P161"/>
+    </x:row>
+    <x:row r="162">
+      <x:c r="K162"/>
+      <x:c r="L162"/>
+      <x:c r="M162"/>
+      <x:c r="N162"/>
+      <x:c r="O162"/>
+      <x:c r="P162"/>
+    </x:row>
+    <x:row r="163">
+      <x:c r="K163"/>
+      <x:c r="L163"/>
+      <x:c r="M163"/>
+      <x:c r="N163"/>
+      <x:c r="O163"/>
+      <x:c r="P163"/>
+    </x:row>
+    <x:row r="164">
+      <x:c r="K164"/>
+      <x:c r="L164"/>
+      <x:c r="M164"/>
+      <x:c r="N164"/>
+      <x:c r="O164"/>
+      <x:c r="P164"/>
+    </x:row>
+    <x:row r="165">
+      <x:c r="K165"/>
+      <x:c r="L165"/>
+      <x:c r="M165"/>
+      <x:c r="N165"/>
+      <x:c r="O165"/>
+      <x:c r="P165"/>
+    </x:row>
+    <x:row r="166">
+      <x:c r="K166"/>
+      <x:c r="L166"/>
+      <x:c r="M166"/>
+      <x:c r="N166"/>
+      <x:c r="O166"/>
+      <x:c r="P166"/>
+    </x:row>
+    <x:row r="167">
+      <x:c r="K167"/>
+      <x:c r="L167"/>
+      <x:c r="M167"/>
+      <x:c r="N167"/>
+      <x:c r="O167"/>
+      <x:c r="P167"/>
+    </x:row>
+    <x:row r="168">
+      <x:c r="K168"/>
+      <x:c r="L168"/>
+      <x:c r="M168"/>
+      <x:c r="N168"/>
+      <x:c r="O168"/>
+      <x:c r="P168"/>
+    </x:row>
+    <x:row r="169">
+      <x:c r="K169"/>
+      <x:c r="L169"/>
+      <x:c r="M169"/>
+      <x:c r="N169"/>
+      <x:c r="O169"/>
+      <x:c r="P169"/>
+    </x:row>
+    <x:row r="170">
+      <x:c r="K170"/>
+      <x:c r="L170"/>
+      <x:c r="M170"/>
+      <x:c r="N170"/>
+      <x:c r="O170"/>
+      <x:c r="P170"/>
+    </x:row>
+    <x:row r="171">
+      <x:c r="K171"/>
+      <x:c r="L171"/>
+      <x:c r="M171"/>
+      <x:c r="N171"/>
+      <x:c r="O171"/>
+      <x:c r="P171"/>
+    </x:row>
+    <x:row r="172">
+      <x:c r="K172"/>
+      <x:c r="L172"/>
+      <x:c r="M172"/>
+      <x:c r="N172"/>
+      <x:c r="O172"/>
+      <x:c r="P172"/>
+    </x:row>
+    <x:row r="173">
+      <x:c r="K173"/>
+      <x:c r="L173"/>
+      <x:c r="M173"/>
+      <x:c r="N173"/>
+      <x:c r="O173"/>
+      <x:c r="P173"/>
+    </x:row>
+    <x:row r="174">
+      <x:c r="K174"/>
+      <x:c r="L174"/>
+      <x:c r="M174"/>
+      <x:c r="N174"/>
+      <x:c r="O174"/>
+      <x:c r="P174"/>
+    </x:row>
+    <x:row r="175">
+      <x:c r="K175"/>
+      <x:c r="L175"/>
+      <x:c r="M175"/>
+      <x:c r="N175"/>
+      <x:c r="O175"/>
+      <x:c r="P175"/>
+    </x:row>
+    <x:row r="176">
+      <x:c r="K176"/>
+      <x:c r="L176"/>
+      <x:c r="M176"/>
+      <x:c r="N176"/>
+      <x:c r="O176"/>
+      <x:c r="P176"/>
+    </x:row>
+    <x:row r="177">
+      <x:c r="K177"/>
+      <x:c r="L177"/>
+      <x:c r="M177"/>
+      <x:c r="N177"/>
+      <x:c r="O177"/>
+      <x:c r="P177"/>
+    </x:row>
+    <x:row r="178">
+      <x:c r="K178"/>
+      <x:c r="L178"/>
+      <x:c r="M178"/>
+      <x:c r="N178"/>
+      <x:c r="O178"/>
+      <x:c r="P178"/>
+    </x:row>
+    <x:row r="179">
+      <x:c r="K179"/>
+      <x:c r="L179"/>
+      <x:c r="M179"/>
+      <x:c r="N179"/>
+      <x:c r="O179"/>
+      <x:c r="P179"/>
+    </x:row>
+    <x:row r="180">
+      <x:c r="K180"/>
+      <x:c r="L180"/>
+      <x:c r="M180"/>
+      <x:c r="N180"/>
+      <x:c r="O180"/>
+      <x:c r="P180"/>
+    </x:row>
+    <x:row r="181">
+      <x:c r="K181"/>
+      <x:c r="L181"/>
+      <x:c r="M181"/>
+      <x:c r="N181"/>
+      <x:c r="O181"/>
+      <x:c r="P181"/>
+    </x:row>
+    <x:row r="182">
+      <x:c r="K182"/>
+      <x:c r="L182"/>
+      <x:c r="M182"/>
+      <x:c r="N182"/>
+      <x:c r="O182"/>
+      <x:c r="P182"/>
+    </x:row>
+    <x:row r="183">
+      <x:c r="K183"/>
+      <x:c r="L183"/>
+      <x:c r="M183"/>
+      <x:c r="N183"/>
+      <x:c r="O183"/>
+      <x:c r="P183"/>
+    </x:row>
+    <x:row r="184">
+      <x:c r="K184"/>
+      <x:c r="L184"/>
+      <x:c r="M184"/>
+      <x:c r="N184"/>
+      <x:c r="O184"/>
+      <x:c r="P184"/>
+    </x:row>
+    <x:row r="185">
+      <x:c r="K185"/>
+      <x:c r="L185"/>
+      <x:c r="M185"/>
+      <x:c r="N185"/>
+      <x:c r="O185"/>
+      <x:c r="P185"/>
+    </x:row>
+    <x:row r="186">
+      <x:c r="K186"/>
+      <x:c r="L186"/>
+      <x:c r="M186"/>
+      <x:c r="N186"/>
+      <x:c r="O186"/>
+      <x:c r="P186"/>
+    </x:row>
+    <x:row r="187">
+      <x:c r="K187"/>
+      <x:c r="L187"/>
+      <x:c r="M187"/>
+      <x:c r="N187"/>
+      <x:c r="O187"/>
+      <x:c r="P187"/>
+    </x:row>
+    <x:row r="188">
+      <x:c r="K188"/>
+      <x:c r="L188"/>
+      <x:c r="M188"/>
+      <x:c r="N188"/>
+      <x:c r="O188"/>
+      <x:c r="P188"/>
+    </x:row>
+    <x:row r="189">
+      <x:c r="K189"/>
+      <x:c r="L189"/>
+      <x:c r="M189"/>
+      <x:c r="N189"/>
+      <x:c r="O189"/>
+      <x:c r="P189"/>
+    </x:row>
+    <x:row r="190">
+      <x:c r="K190"/>
+      <x:c r="L190"/>
+      <x:c r="M190"/>
+      <x:c r="N190"/>
+      <x:c r="O190"/>
+      <x:c r="P190"/>
+    </x:row>
+    <x:row r="191">
+      <x:c r="K191"/>
+      <x:c r="L191"/>
+      <x:c r="M191"/>
+      <x:c r="N191"/>
+      <x:c r="O191"/>
+      <x:c r="P191"/>
+    </x:row>
+    <x:row r="192">
+      <x:c r="K192"/>
+      <x:c r="L192"/>
+      <x:c r="M192"/>
+      <x:c r="N192"/>
+      <x:c r="O192"/>
+      <x:c r="P192"/>
+    </x:row>
+    <x:row r="193">
+      <x:c r="K193"/>
+      <x:c r="L193"/>
+      <x:c r="M193"/>
+      <x:c r="N193"/>
+      <x:c r="O193"/>
+      <x:c r="P193"/>
+    </x:row>
+    <x:row r="194">
+      <x:c r="K194"/>
+      <x:c r="L194"/>
+      <x:c r="M194"/>
+      <x:c r="N194"/>
+      <x:c r="O194"/>
+      <x:c r="P194"/>
+    </x:row>
+    <x:row r="195">
+      <x:c r="K195"/>
+      <x:c r="L195"/>
+      <x:c r="M195"/>
+      <x:c r="N195"/>
+      <x:c r="O195"/>
+      <x:c r="P195"/>
+    </x:row>
+    <x:row r="196">
+      <x:c r="K196"/>
+      <x:c r="L196"/>
+      <x:c r="M196"/>
+      <x:c r="N196"/>
+      <x:c r="O196"/>
+      <x:c r="P196"/>
+    </x:row>
+    <x:row r="197">
+      <x:c r="K197"/>
+      <x:c r="L197"/>
+      <x:c r="M197"/>
+      <x:c r="N197"/>
+      <x:c r="O197"/>
+      <x:c r="P197"/>
+    </x:row>
+    <x:row r="198">
+      <x:c r="K198"/>
+      <x:c r="L198"/>
+      <x:c r="M198"/>
+      <x:c r="N198"/>
+      <x:c r="O198"/>
+      <x:c r="P198"/>
+    </x:row>
+    <x:row r="199">
+      <x:c r="K199"/>
+      <x:c r="L199"/>
+      <x:c r="M199"/>
+      <x:c r="N199"/>
+      <x:c r="O199"/>
+      <x:c r="P199"/>
+    </x:row>
+    <x:row r="200">
+      <x:c r="K200"/>
+      <x:c r="L200"/>
+      <x:c r="M200"/>
+      <x:c r="N200"/>
+      <x:c r="O200"/>
+      <x:c r="P200"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
